--- a/Outputs/Scenarios/PtX_demand_EL_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_EL_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0001121986657946518</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01082051566475977</v>
+        <v>0.006063910908582124</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.003606838554919922</v>
+        <v>0.008379197306212241</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>1.61659285361267e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.003606838554919922</v>
+        <v>0.003591084559805246</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0001660964649254383</v>
       </c>
       <c r="K30" t="n">
-        <v>0.05826846776728018</v>
+        <v>0.03265415515002822</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.01942282258909339</v>
+        <v>0.04512197045680712</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>8.741919206602016e-06</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01942282258909339</v>
+        <v>0.01933798733863162</v>
       </c>
     </row>
     <row r="43">
